--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-18 11:51:46 UTC</t>
+    <t>2026-06-18 12:25:41 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-18 12:25:41 UTC</t>
+    <t>2026-06-18 13:08:37 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-18 13:08:37 UTC</t>
+    <t>2026-06-18 13:36:08 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-18 13:36:08 UTC</t>
+    <t>2026-06-18 14:09:54 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-18 14:09:54 UTC</t>
+    <t>2026-06-18 17:47:53 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-18 17:47:53 UTC</t>
+    <t>2026-06-19 06:37:38 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-19 06:37:38 UTC</t>
+    <t>2026-06-19 07:01:21 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-19 07:01:21 UTC</t>
+    <t>2026-06-19 08:52:59 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-19 08:52:59 UTC</t>
+    <t>2026-06-19 12:37:03 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-19 12:37:03 UTC</t>
+    <t>2026-06-20 07:19:01 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-20 07:19:01 UTC</t>
+    <t>2026-06-20 07:42:47 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-20 07:42:47 UTC</t>
+    <t>2026-06-21 10:30:48 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-21 10:30:48 UTC</t>
+    <t>2026-06-22 03:58:38 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 03:58:38 UTC</t>
+    <t>2026-06-22 04:41:09 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 04:41:09 UTC</t>
+    <t>2026-06-22 05:59:17 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 05:59:17 UTC</t>
+    <t>2026-06-22 06:47:02 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 06:47:02 UTC</t>
+    <t>2026-06-22 07:27:47 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 07:27:47 UTC</t>
+    <t>2026-06-22 08:31:20 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 08:31:20 UTC</t>
+    <t>2026-06-22 09:17:50 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>21</t>
+    <t>22</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 09:17:50 UTC</t>
+    <t>2026-06-22 10:09:12 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 10:09:12 UTC</t>
+    <t>2026-06-22 11:55:55 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 11:55:55 UTC</t>
+    <t>2026-06-22 12:29:25 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>24</t>
+    <t>25</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 12:29:25 UTC</t>
+    <t>2026-06-22 13:00:51 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 13:00:51 UTC</t>
+    <t>2026-06-22 13:42:36 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 13:42:36 UTC</t>
+    <t>2026-06-22 14:18:00 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 14:18:00 UTC</t>
+    <t>2026-06-22 14:41:32 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 14:41:32 UTC</t>
+    <t>2026-06-22 16:48:58 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>29</t>
+    <t>30</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -283,13 +283,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-22 16:48:58 UTC</t>
+    <t>2026-06-23 07:45:09 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>30</t>
+    <t>31</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>
